--- a/Question_Bank_Bulk_PDF_Metadata_Template.xlsx
+++ b/Question_Bank_Bulk_PDF_Metadata_Template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,6 +29,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -56,13 +59,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -429,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -444,47 +453,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Page No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Chapter No</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Subchapter No</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Chapter Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Question Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Cognitive Level</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Difficulty</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Correct Answer</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -497,35 +511,36 @@
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Number System</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Correct answer is 4.</t>
         </is>
@@ -538,35 +553,35 @@
       <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Number System</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Question_Bank_Bulk_PDF_Metadata_Template.xlsx
+++ b/Question_Bank_Bulk_PDF_Metadata_Template.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -503,6 +503,11 @@
           <t>Explanation</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Variation Group</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -511,7 +516,6 @@
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Number System</t>
@@ -545,6 +549,7 @@
           <t>Correct answer is 4.</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">

--- a/Question_Bank_Bulk_PDF_Metadata_Template.xlsx
+++ b/Question_Bank_Bulk_PDF_Metadata_Template.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -508,6 +508,11 @@
           <t>Variation Group</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Fixed Question</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -549,7 +554,11 @@
           <t>Correct answer is 4.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">

--- a/Question_Bank_Bulk_PDF_Metadata_Template.xlsx
+++ b/Question_Bank_Bulk_PDF_Metadata_Template.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -510,6 +510,11 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Lesson / Topic</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>Fixed Question</t>
         </is>
       </c>
@@ -555,6 +560,11 @@
         </is>
       </c>
       <c r="L2" t="inlineStr">
+        <is>
+          <t>Example: Addition of Unlike Fractions</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/Question_Bank_Bulk_PDF_Metadata_Template.xlsx
+++ b/Question_Bank_Bulk_PDF_Metadata_Template.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -453,52 +453,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Page No</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Chapter No</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Subchapter No</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Chapter Name</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Question Type</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Cognitive Level</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Difficulty</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Correct Answer</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -518,43 +518,53 @@
           <t>Fixed Question</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Text_Book</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Textbook_Reference</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Number System</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Correct answer is 4.</t>
         </is>
@@ -571,41 +581,40 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Number System</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Question_Bank_Bulk_PDF_Metadata_Template.xlsx
+++ b/Question_Bank_Bulk_PDF_Metadata_Template.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -475,55 +475,60 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Question Type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Cognitive Level</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Difficulty</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Correct Answer</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Variation Group</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Lesson / Topic</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Fixed Question</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Text_Book</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Textbook_Reference</t>
         </is>
@@ -543,38 +548,43 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Correct answer is 4.</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Example: Addition of Unlike Fractions</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -592,25 +602,25 @@
           <t>Number System</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
